--- a/Codelist Excel Files and Conversion Templates to XML/direction.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/direction.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Codes for the direction a geosynthetic's stiffness, strength, tension or installed orientation is stated in - machine, cross-machine, or isotropic. Shared vocabulary between the design value (diggs:GeosyntheticLayerDesignType/diggs:direction) and the as-built value (diggs:GeosyntheticType/diggs:direction) so an installed layer's stated orientation can be compared against the design value that governs it - same pattern as diggs:columnType (S6).</t>
+          <t>Codes for the direction a geosynthetic's stiffness, strength, tension or installed orientation is stated in - machine, cross-machine, or isotropic. Shared vocabulary between the design value (diggs:DesignGeosyntheticLayerType/diggs:direction) and the as-built value (diggs:GeosyntheticType/diggs:direction) so an installed layer's stated orientation can be compared against the design value that governs it - same pattern as diggs:columnType (S6).</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>//diggs:GeosyntheticLayerDesign/diggs:direction</t>
+          <t>//diggs:DesignGeosyntheticLayer/diggs:direction</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>//diggs:GeosyntheticLayerDesign/diggs:direction</t>
+          <t>//diggs:DesignGeosyntheticLayer/diggs:direction</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>//diggs:GeosyntheticLayerDesign/diggs:direction</t>
+          <t>//diggs:DesignGeosyntheticLayer/diggs:direction</t>
         </is>
       </c>
     </row>
